--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,2026 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128369628</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96725</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>53</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>545520</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6960544</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128369612</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>545441</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6960551</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128369610</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>545456</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6960552</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128369619</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>545518</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6960573</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128369627</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>545576</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6960564</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128369616</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79649</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>545485</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6960542</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128369614</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78789</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>545454</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6960547</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128369615</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78789</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>545483</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6960539</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128369611</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>545452</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6960544</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128369621</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>545545</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6960571</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128369626</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78789</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>545578</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6960574</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128369624</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>545590</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6960568</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128369620</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90390</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>545519</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6960567</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128369623</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>545593</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6960594</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128369613</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>545435</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6960538</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128369618</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>545491</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6960549</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128369617</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78698</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>353</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>545487</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6960539</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128369622</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>545561</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6960584</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128369625</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>545585</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6960570</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128369609</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92645</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>545443</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6960571</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -2618,7 +2618,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128369625</v>
+        <v>128369609</v>
       </c>
       <c r="B21" t="n">
         <v>92645</v>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545585</v>
+        <v>545443</v>
       </c>
       <c r="R21" t="n">
-        <v>6960570</v>
+        <v>6960571</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2719,7 +2719,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128369609</v>
+        <v>128369625</v>
       </c>
       <c r="B22" t="n">
         <v>92645</v>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545443</v>
+        <v>545585</v>
       </c>
       <c r="R22" t="n">
-        <v>6960571</v>
+        <v>6960570</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -1810,32 +1810,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128369626</v>
+        <v>128369624</v>
       </c>
       <c r="B13" t="n">
-        <v>78789</v>
+        <v>92645</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545578</v>
+        <v>545590</v>
       </c>
       <c r="R13" t="n">
-        <v>6960574</v>
+        <v>6960568</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1911,32 +1911,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128369624</v>
+        <v>128369620</v>
       </c>
       <c r="B14" t="n">
-        <v>92645</v>
+        <v>90390</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545590</v>
+        <v>545519</v>
       </c>
       <c r="R14" t="n">
-        <v>6960568</v>
+        <v>6960567</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128369620</v>
+        <v>128369626</v>
       </c>
       <c r="B15" t="n">
-        <v>90390</v>
+        <v>78789</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545519</v>
+        <v>545578</v>
       </c>
       <c r="R15" t="n">
-        <v>6960567</v>
+        <v>6960574</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -1810,32 +1810,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128369624</v>
+        <v>128369626</v>
       </c>
       <c r="B13" t="n">
-        <v>92645</v>
+        <v>78789</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545590</v>
+        <v>545578</v>
       </c>
       <c r="R13" t="n">
-        <v>6960568</v>
+        <v>6960574</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1911,32 +1911,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128369620</v>
+        <v>128369624</v>
       </c>
       <c r="B14" t="n">
-        <v>90390</v>
+        <v>92645</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545519</v>
+        <v>545590</v>
       </c>
       <c r="R14" t="n">
-        <v>6960567</v>
+        <v>6960568</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128369626</v>
+        <v>128369620</v>
       </c>
       <c r="B15" t="n">
-        <v>78789</v>
+        <v>90390</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545578</v>
+        <v>545519</v>
       </c>
       <c r="R15" t="n">
-        <v>6960574</v>
+        <v>6960567</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -1810,32 +1810,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128369626</v>
+        <v>128369624</v>
       </c>
       <c r="B13" t="n">
-        <v>78789</v>
+        <v>92645</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545578</v>
+        <v>545590</v>
       </c>
       <c r="R13" t="n">
-        <v>6960574</v>
+        <v>6960568</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1911,32 +1911,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128369624</v>
+        <v>128369620</v>
       </c>
       <c r="B14" t="n">
-        <v>92645</v>
+        <v>90390</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545590</v>
+        <v>545519</v>
       </c>
       <c r="R14" t="n">
-        <v>6960568</v>
+        <v>6960567</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128369620</v>
+        <v>128369626</v>
       </c>
       <c r="B15" t="n">
-        <v>90390</v>
+        <v>78789</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545519</v>
+        <v>545578</v>
       </c>
       <c r="R15" t="n">
-        <v>6960567</v>
+        <v>6960574</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2618,7 +2618,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128369609</v>
+        <v>128369625</v>
       </c>
       <c r="B21" t="n">
         <v>92645</v>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545443</v>
+        <v>545585</v>
       </c>
       <c r="R21" t="n">
-        <v>6960571</v>
+        <v>6960570</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2719,7 +2719,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128369625</v>
+        <v>128369609</v>
       </c>
       <c r="B22" t="n">
         <v>92645</v>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545585</v>
+        <v>545443</v>
       </c>
       <c r="R22" t="n">
-        <v>6960570</v>
+        <v>6960571</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -800,32 +800,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369628</v>
+        <v>128369612</v>
       </c>
       <c r="B3" t="n">
-        <v>96725</v>
+        <v>92650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545520</v>
+        <v>545441</v>
       </c>
       <c r="R3" t="n">
-        <v>6960544</v>
+        <v>6960551</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128369612</v>
+        <v>128369628</v>
       </c>
       <c r="B4" t="n">
-        <v>92645</v>
+        <v>96730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545441</v>
+        <v>545520</v>
       </c>
       <c r="R4" t="n">
-        <v>6960551</v>
+        <v>6960544</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1005,7 +1005,7 @@
         <v>128369610</v>
       </c>
       <c r="B5" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128369619</v>
       </c>
       <c r="B6" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>128369627</v>
       </c>
       <c r="B7" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>128369616</v>
       </c>
       <c r="B8" t="n">
-        <v>79649</v>
+        <v>79650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,10 +1406,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128369614</v>
+        <v>128369615</v>
       </c>
       <c r="B9" t="n">
-        <v>78789</v>
+        <v>78790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545454</v>
+        <v>545483</v>
       </c>
       <c r="R9" t="n">
-        <v>6960547</v>
+        <v>6960539</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128369615</v>
+        <v>128369614</v>
       </c>
       <c r="B10" t="n">
-        <v>78789</v>
+        <v>78790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545483</v>
+        <v>545454</v>
       </c>
       <c r="R10" t="n">
-        <v>6960539</v>
+        <v>6960547</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,7 +1611,7 @@
         <v>128369611</v>
       </c>
       <c r="B11" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>128369621</v>
       </c>
       <c r="B12" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,32 +1810,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128369624</v>
+        <v>128369626</v>
       </c>
       <c r="B13" t="n">
-        <v>92645</v>
+        <v>78790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545590</v>
+        <v>545578</v>
       </c>
       <c r="R13" t="n">
-        <v>6960568</v>
+        <v>6960574</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1914,7 +1914,7 @@
         <v>128369620</v>
       </c>
       <c r="B14" t="n">
-        <v>90390</v>
+        <v>90393</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2012,32 +2012,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128369626</v>
+        <v>128369624</v>
       </c>
       <c r="B15" t="n">
-        <v>78789</v>
+        <v>92650</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545578</v>
+        <v>545590</v>
       </c>
       <c r="R15" t="n">
-        <v>6960574</v>
+        <v>6960568</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2116,7 +2116,7 @@
         <v>128369623</v>
       </c>
       <c r="B16" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128369613</v>
+        <v>128369618</v>
       </c>
       <c r="B17" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545435</v>
+        <v>545491</v>
       </c>
       <c r="R17" t="n">
-        <v>6960538</v>
+        <v>6960549</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2315,10 +2315,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128369618</v>
+        <v>128369613</v>
       </c>
       <c r="B18" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545491</v>
+        <v>545435</v>
       </c>
       <c r="R18" t="n">
-        <v>6960549</v>
+        <v>6960538</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2419,7 +2419,7 @@
         <v>128369617</v>
       </c>
       <c r="B19" t="n">
-        <v>78698</v>
+        <v>78699</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>128369622</v>
       </c>
       <c r="B20" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>128369625</v>
       </c>
       <c r="B21" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>128369609</v>
       </c>
       <c r="B22" t="n">
-        <v>92645</v>
+        <v>92650</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -1810,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128369626</v>
+        <v>128369620</v>
       </c>
       <c r="B13" t="n">
-        <v>78790</v>
+        <v>90393</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1821,21 +1821,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545578</v>
+        <v>545519</v>
       </c>
       <c r="R13" t="n">
-        <v>6960574</v>
+        <v>6960567</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1911,32 +1911,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128369620</v>
+        <v>128369624</v>
       </c>
       <c r="B14" t="n">
-        <v>90393</v>
+        <v>92650</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545519</v>
+        <v>545590</v>
       </c>
       <c r="R14" t="n">
-        <v>6960567</v>
+        <v>6960568</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2012,32 +2012,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128369624</v>
+        <v>128369626</v>
       </c>
       <c r="B15" t="n">
-        <v>92650</v>
+        <v>78790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545590</v>
+        <v>545578</v>
       </c>
       <c r="R15" t="n">
-        <v>6960568</v>
+        <v>6960574</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -800,32 +800,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369612</v>
+        <v>128369628</v>
       </c>
       <c r="B3" t="n">
-        <v>92650</v>
+        <v>96823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545441</v>
+        <v>545520</v>
       </c>
       <c r="R3" t="n">
-        <v>6960551</v>
+        <v>6960544</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128369628</v>
+        <v>128369612</v>
       </c>
       <c r="B4" t="n">
-        <v>96730</v>
+        <v>92742</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545520</v>
+        <v>545441</v>
       </c>
       <c r="R4" t="n">
-        <v>6960544</v>
+        <v>6960551</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1005,7 +1005,7 @@
         <v>128369610</v>
       </c>
       <c r="B5" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128369619</v>
+        <v>128369627</v>
       </c>
       <c r="B6" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545518</v>
+        <v>545576</v>
       </c>
       <c r="R6" t="n">
-        <v>6960573</v>
+        <v>6960564</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128369627</v>
+        <v>128369619</v>
       </c>
       <c r="B7" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545576</v>
+        <v>545518</v>
       </c>
       <c r="R7" t="n">
-        <v>6960564</v>
+        <v>6960573</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1308,7 +1308,7 @@
         <v>128369616</v>
       </c>
       <c r="B8" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>128369615</v>
       </c>
       <c r="B9" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>128369614</v>
       </c>
       <c r="B10" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128369611</v>
       </c>
       <c r="B11" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>128369621</v>
       </c>
       <c r="B12" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,32 +1810,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128369620</v>
+        <v>128369624</v>
       </c>
       <c r="B13" t="n">
-        <v>90393</v>
+        <v>92742</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545519</v>
+        <v>545590</v>
       </c>
       <c r="R13" t="n">
-        <v>6960567</v>
+        <v>6960568</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1911,32 +1911,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128369624</v>
+        <v>128369626</v>
       </c>
       <c r="B14" t="n">
-        <v>92650</v>
+        <v>78840</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545590</v>
+        <v>545578</v>
       </c>
       <c r="R14" t="n">
-        <v>6960568</v>
+        <v>6960574</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128369626</v>
+        <v>128369620</v>
       </c>
       <c r="B15" t="n">
-        <v>78790</v>
+        <v>90485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545578</v>
+        <v>545519</v>
       </c>
       <c r="R15" t="n">
-        <v>6960574</v>
+        <v>6960567</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2116,7 +2116,7 @@
         <v>128369623</v>
       </c>
       <c r="B16" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>128369618</v>
       </c>
       <c r="B17" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>128369613</v>
       </c>
       <c r="B18" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>128369617</v>
       </c>
       <c r="B19" t="n">
-        <v>78699</v>
+        <v>78749</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>128369622</v>
       </c>
       <c r="B20" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>128369625</v>
       </c>
       <c r="B21" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>128369609</v>
       </c>
       <c r="B22" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -800,32 +800,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369628</v>
+        <v>128369612</v>
       </c>
       <c r="B3" t="n">
-        <v>96823</v>
+        <v>92742</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545520</v>
+        <v>545441</v>
       </c>
       <c r="R3" t="n">
-        <v>6960544</v>
+        <v>6960551</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128369612</v>
+        <v>128369628</v>
       </c>
       <c r="B4" t="n">
-        <v>92742</v>
+        <v>96823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545441</v>
+        <v>545520</v>
       </c>
       <c r="R4" t="n">
-        <v>6960551</v>
+        <v>6960544</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128369610</v>
+        <v>128369619</v>
       </c>
       <c r="B5" t="n">
         <v>92742</v>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545456</v>
+        <v>545518</v>
       </c>
       <c r="R5" t="n">
-        <v>6960552</v>
+        <v>6960573</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128369627</v>
+        <v>128369610</v>
       </c>
       <c r="B6" t="n">
         <v>92742</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545576</v>
+        <v>545456</v>
       </c>
       <c r="R6" t="n">
-        <v>6960564</v>
+        <v>6960552</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,7 +1204,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128369619</v>
+        <v>128369627</v>
       </c>
       <c r="B7" t="n">
         <v>92742</v>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545518</v>
+        <v>545576</v>
       </c>
       <c r="R7" t="n">
-        <v>6960573</v>
+        <v>6960564</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1406,7 +1406,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128369615</v>
+        <v>128369614</v>
       </c>
       <c r="B9" t="n">
         <v>78840</v>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545483</v>
+        <v>545454</v>
       </c>
       <c r="R9" t="n">
-        <v>6960539</v>
+        <v>6960547</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1507,7 +1507,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128369614</v>
+        <v>128369615</v>
       </c>
       <c r="B10" t="n">
         <v>78840</v>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545454</v>
+        <v>545483</v>
       </c>
       <c r="R10" t="n">
-        <v>6960547</v>
+        <v>6960539</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1810,32 +1810,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128369624</v>
+        <v>128369626</v>
       </c>
       <c r="B13" t="n">
-        <v>92742</v>
+        <v>78840</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545590</v>
+        <v>545578</v>
       </c>
       <c r="R13" t="n">
-        <v>6960568</v>
+        <v>6960574</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1911,10 +1911,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128369626</v>
+        <v>128369620</v>
       </c>
       <c r="B14" t="n">
-        <v>78840</v>
+        <v>90485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1922,21 +1922,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545578</v>
+        <v>545519</v>
       </c>
       <c r="R14" t="n">
-        <v>6960574</v>
+        <v>6960567</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2012,32 +2012,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128369620</v>
+        <v>128369624</v>
       </c>
       <c r="B15" t="n">
-        <v>90485</v>
+        <v>92742</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545519</v>
+        <v>545590</v>
       </c>
       <c r="R15" t="n">
-        <v>6960567</v>
+        <v>6960568</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -1002,7 +1002,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128369619</v>
+        <v>128369610</v>
       </c>
       <c r="B5" t="n">
         <v>92742</v>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545518</v>
+        <v>545456</v>
       </c>
       <c r="R5" t="n">
-        <v>6960573</v>
+        <v>6960552</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128369610</v>
+        <v>128369619</v>
       </c>
       <c r="B6" t="n">
         <v>92742</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545456</v>
+        <v>545518</v>
       </c>
       <c r="R6" t="n">
-        <v>6960552</v>
+        <v>6960573</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1810,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128369626</v>
+        <v>128369620</v>
       </c>
       <c r="B13" t="n">
-        <v>78840</v>
+        <v>90485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1821,21 +1821,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545578</v>
+        <v>545519</v>
       </c>
       <c r="R13" t="n">
-        <v>6960574</v>
+        <v>6960567</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1911,32 +1911,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128369620</v>
+        <v>128369624</v>
       </c>
       <c r="B14" t="n">
-        <v>90485</v>
+        <v>92742</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545519</v>
+        <v>545590</v>
       </c>
       <c r="R14" t="n">
-        <v>6960567</v>
+        <v>6960568</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2012,32 +2012,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128369624</v>
+        <v>128369626</v>
       </c>
       <c r="B15" t="n">
-        <v>92742</v>
+        <v>78840</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545590</v>
+        <v>545578</v>
       </c>
       <c r="R15" t="n">
-        <v>6960568</v>
+        <v>6960574</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128369614</v>
+        <v>128369615</v>
       </c>
       <c r="B9" t="n">
         <v>78840</v>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545454</v>
+        <v>545483</v>
       </c>
       <c r="R9" t="n">
-        <v>6960547</v>
+        <v>6960539</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1507,7 +1507,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128369615</v>
+        <v>128369614</v>
       </c>
       <c r="B10" t="n">
         <v>78840</v>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545483</v>
+        <v>545454</v>
       </c>
       <c r="R10" t="n">
-        <v>6960539</v>
+        <v>6960547</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1810,32 +1810,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128369620</v>
+        <v>128369624</v>
       </c>
       <c r="B13" t="n">
-        <v>90485</v>
+        <v>92742</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545519</v>
+        <v>545590</v>
       </c>
       <c r="R13" t="n">
-        <v>6960567</v>
+        <v>6960568</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1911,32 +1911,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128369624</v>
+        <v>128369626</v>
       </c>
       <c r="B14" t="n">
-        <v>92742</v>
+        <v>78840</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545590</v>
+        <v>545578</v>
       </c>
       <c r="R14" t="n">
-        <v>6960568</v>
+        <v>6960574</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128369626</v>
+        <v>128369620</v>
       </c>
       <c r="B15" t="n">
-        <v>78840</v>
+        <v>90485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545578</v>
+        <v>545519</v>
       </c>
       <c r="R15" t="n">
-        <v>6960574</v>
+        <v>6960567</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -800,32 +800,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369612</v>
+        <v>128369628</v>
       </c>
       <c r="B3" t="n">
-        <v>92742</v>
+        <v>96835</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545441</v>
+        <v>545520</v>
       </c>
       <c r="R3" t="n">
-        <v>6960551</v>
+        <v>6960544</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128369628</v>
+        <v>128369612</v>
       </c>
       <c r="B4" t="n">
-        <v>96823</v>
+        <v>92754</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545520</v>
+        <v>545441</v>
       </c>
       <c r="R4" t="n">
-        <v>6960544</v>
+        <v>6960551</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1005,7 +1005,7 @@
         <v>128369610</v>
       </c>
       <c r="B5" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128369619</v>
       </c>
       <c r="B6" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>128369627</v>
       </c>
       <c r="B7" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>128369616</v>
       </c>
       <c r="B8" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>128369615</v>
       </c>
       <c r="B9" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>128369614</v>
       </c>
       <c r="B10" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128369611</v>
       </c>
       <c r="B11" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>128369621</v>
       </c>
       <c r="B12" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,32 +1810,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128369624</v>
+        <v>128369620</v>
       </c>
       <c r="B13" t="n">
-        <v>92742</v>
+        <v>90497</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545590</v>
+        <v>545519</v>
       </c>
       <c r="R13" t="n">
-        <v>6960568</v>
+        <v>6960567</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1914,7 +1914,7 @@
         <v>128369626</v>
       </c>
       <c r="B14" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2012,32 +2012,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128369620</v>
+        <v>128369624</v>
       </c>
       <c r="B15" t="n">
-        <v>90485</v>
+        <v>92754</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545519</v>
+        <v>545590</v>
       </c>
       <c r="R15" t="n">
-        <v>6960567</v>
+        <v>6960568</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2116,7 +2116,7 @@
         <v>128369623</v>
       </c>
       <c r="B16" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>128369618</v>
       </c>
       <c r="B17" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>128369613</v>
       </c>
       <c r="B18" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>128369617</v>
       </c>
       <c r="B19" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>128369622</v>
       </c>
       <c r="B20" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>128369625</v>
       </c>
       <c r="B21" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>128369609</v>
       </c>
       <c r="B22" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -800,32 +800,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369628</v>
+        <v>128369612</v>
       </c>
       <c r="B3" t="n">
-        <v>96835</v>
+        <v>92756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545520</v>
+        <v>545441</v>
       </c>
       <c r="R3" t="n">
-        <v>6960544</v>
+        <v>6960551</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128369612</v>
+        <v>128369628</v>
       </c>
       <c r="B4" t="n">
-        <v>92754</v>
+        <v>96837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545441</v>
+        <v>545520</v>
       </c>
       <c r="R4" t="n">
-        <v>6960551</v>
+        <v>6960544</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1005,7 +1005,7 @@
         <v>128369610</v>
       </c>
       <c r="B5" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128369619</v>
       </c>
       <c r="B6" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>128369627</v>
       </c>
       <c r="B7" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>128369616</v>
       </c>
       <c r="B8" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>128369615</v>
       </c>
       <c r="B9" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>128369614</v>
       </c>
       <c r="B10" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128369611</v>
       </c>
       <c r="B11" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>128369621</v>
       </c>
       <c r="B12" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,32 +1810,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128369620</v>
+        <v>128369624</v>
       </c>
       <c r="B13" t="n">
-        <v>90497</v>
+        <v>92756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545519</v>
+        <v>545590</v>
       </c>
       <c r="R13" t="n">
-        <v>6960567</v>
+        <v>6960568</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1911,10 +1911,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128369626</v>
+        <v>128369620</v>
       </c>
       <c r="B14" t="n">
-        <v>78844</v>
+        <v>90499</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1922,21 +1922,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545578</v>
+        <v>545519</v>
       </c>
       <c r="R14" t="n">
-        <v>6960574</v>
+        <v>6960567</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2012,32 +2012,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128369624</v>
+        <v>128369626</v>
       </c>
       <c r="B15" t="n">
-        <v>92754</v>
+        <v>78846</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545590</v>
+        <v>545578</v>
       </c>
       <c r="R15" t="n">
-        <v>6960568</v>
+        <v>6960574</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2116,7 +2116,7 @@
         <v>128369623</v>
       </c>
       <c r="B16" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>128369618</v>
       </c>
       <c r="B17" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>128369613</v>
       </c>
       <c r="B18" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>128369617</v>
       </c>
       <c r="B19" t="n">
-        <v>78753</v>
+        <v>78755</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>128369622</v>
       </c>
       <c r="B20" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>128369625</v>
       </c>
       <c r="B21" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>128369609</v>
       </c>
       <c r="B22" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -800,32 +800,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369612</v>
+        <v>128369628</v>
       </c>
       <c r="B3" t="n">
-        <v>92756</v>
+        <v>96837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545441</v>
+        <v>545520</v>
       </c>
       <c r="R3" t="n">
-        <v>6960551</v>
+        <v>6960544</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128369628</v>
+        <v>128369612</v>
       </c>
       <c r="B4" t="n">
-        <v>96837</v>
+        <v>92756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545520</v>
+        <v>545441</v>
       </c>
       <c r="R4" t="n">
-        <v>6960544</v>
+        <v>6960551</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128369628</v>
       </c>
       <c r="B3" t="n">
-        <v>96837</v>
+        <v>96838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>128369612</v>
       </c>
       <c r="B4" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>128369610</v>
       </c>
       <c r="B5" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128369619</v>
       </c>
       <c r="B6" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>128369627</v>
       </c>
       <c r="B7" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128369615</v>
+        <v>128369614</v>
       </c>
       <c r="B9" t="n">
         <v>78846</v>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545483</v>
+        <v>545454</v>
       </c>
       <c r="R9" t="n">
-        <v>6960539</v>
+        <v>6960547</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1507,7 +1507,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128369614</v>
+        <v>128369615</v>
       </c>
       <c r="B10" t="n">
         <v>78846</v>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545454</v>
+        <v>545483</v>
       </c>
       <c r="R10" t="n">
-        <v>6960547</v>
+        <v>6960539</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,7 +1611,7 @@
         <v>128369611</v>
       </c>
       <c r="B11" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>128369621</v>
       </c>
       <c r="B12" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>128369624</v>
       </c>
       <c r="B13" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>128369623</v>
       </c>
       <c r="B16" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>128369618</v>
       </c>
       <c r="B17" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>128369613</v>
       </c>
       <c r="B18" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>128369622</v>
       </c>
       <c r="B20" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>128369625</v>
       </c>
       <c r="B21" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>128369609</v>
       </c>
       <c r="B22" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128369628</v>
       </c>
       <c r="B3" t="n">
-        <v>96838</v>
+        <v>96865</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>128369612</v>
       </c>
       <c r="B4" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128369610</v>
+        <v>128369627</v>
       </c>
       <c r="B5" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545456</v>
+        <v>545576</v>
       </c>
       <c r="R5" t="n">
-        <v>6960552</v>
+        <v>6960564</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128369619</v>
+        <v>128369610</v>
       </c>
       <c r="B6" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545518</v>
+        <v>545456</v>
       </c>
       <c r="R6" t="n">
-        <v>6960573</v>
+        <v>6960552</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128369627</v>
+        <v>128369619</v>
       </c>
       <c r="B7" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545576</v>
+        <v>545518</v>
       </c>
       <c r="R7" t="n">
-        <v>6960564</v>
+        <v>6960573</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1308,7 +1308,7 @@
         <v>128369616</v>
       </c>
       <c r="B8" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,10 +1406,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128369614</v>
+        <v>128369615</v>
       </c>
       <c r="B9" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545454</v>
+        <v>545483</v>
       </c>
       <c r="R9" t="n">
-        <v>6960547</v>
+        <v>6960539</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128369615</v>
+        <v>128369614</v>
       </c>
       <c r="B10" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545483</v>
+        <v>545454</v>
       </c>
       <c r="R10" t="n">
-        <v>6960539</v>
+        <v>6960547</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,7 +1611,7 @@
         <v>128369611</v>
       </c>
       <c r="B11" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>128369621</v>
       </c>
       <c r="B12" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,32 +1810,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128369624</v>
+        <v>128369620</v>
       </c>
       <c r="B13" t="n">
-        <v>92757</v>
+        <v>90526</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545590</v>
+        <v>545519</v>
       </c>
       <c r="R13" t="n">
-        <v>6960568</v>
+        <v>6960567</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1911,32 +1911,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128369620</v>
+        <v>128369624</v>
       </c>
       <c r="B14" t="n">
-        <v>90499</v>
+        <v>92784</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545519</v>
+        <v>545590</v>
       </c>
       <c r="R14" t="n">
-        <v>6960567</v>
+        <v>6960568</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2015,7 +2015,7 @@
         <v>128369626</v>
       </c>
       <c r="B15" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>128369623</v>
       </c>
       <c r="B16" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128369618</v>
+        <v>128369613</v>
       </c>
       <c r="B17" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545491</v>
+        <v>545435</v>
       </c>
       <c r="R17" t="n">
-        <v>6960549</v>
+        <v>6960538</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2315,10 +2315,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128369613</v>
+        <v>128369618</v>
       </c>
       <c r="B18" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545435</v>
+        <v>545491</v>
       </c>
       <c r="R18" t="n">
-        <v>6960538</v>
+        <v>6960549</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2419,7 +2419,7 @@
         <v>128369617</v>
       </c>
       <c r="B19" t="n">
-        <v>78755</v>
+        <v>78782</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>128369622</v>
       </c>
       <c r="B20" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>128369625</v>
       </c>
       <c r="B21" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>128369609</v>
       </c>
       <c r="B22" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -1002,7 +1002,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128369627</v>
+        <v>128369610</v>
       </c>
       <c r="B5" t="n">
         <v>92784</v>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545576</v>
+        <v>545456</v>
       </c>
       <c r="R5" t="n">
-        <v>6960564</v>
+        <v>6960552</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128369610</v>
+        <v>128369619</v>
       </c>
       <c r="B6" t="n">
         <v>92784</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545456</v>
+        <v>545518</v>
       </c>
       <c r="R6" t="n">
-        <v>6960552</v>
+        <v>6960573</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,7 +1204,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128369619</v>
+        <v>128369627</v>
       </c>
       <c r="B7" t="n">
         <v>92784</v>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545518</v>
+        <v>545576</v>
       </c>
       <c r="R7" t="n">
-        <v>6960573</v>
+        <v>6960564</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1911,32 +1911,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128369624</v>
+        <v>128369626</v>
       </c>
       <c r="B14" t="n">
-        <v>92784</v>
+        <v>78873</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545590</v>
+        <v>545578</v>
       </c>
       <c r="R14" t="n">
-        <v>6960568</v>
+        <v>6960574</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2012,32 +2012,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128369626</v>
+        <v>128369624</v>
       </c>
       <c r="B15" t="n">
-        <v>78873</v>
+        <v>92784</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545578</v>
+        <v>545590</v>
       </c>
       <c r="R15" t="n">
-        <v>6960574</v>
+        <v>6960568</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2214,7 +2214,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128369613</v>
+        <v>128369618</v>
       </c>
       <c r="B17" t="n">
         <v>92784</v>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545435</v>
+        <v>545491</v>
       </c>
       <c r="R17" t="n">
-        <v>6960538</v>
+        <v>6960549</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2315,7 +2315,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128369618</v>
+        <v>128369613</v>
       </c>
       <c r="B18" t="n">
         <v>92784</v>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545491</v>
+        <v>545435</v>
       </c>
       <c r="R18" t="n">
-        <v>6960549</v>
+        <v>6960538</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128369628</v>
       </c>
       <c r="B3" t="n">
-        <v>96865</v>
+        <v>96878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>128369612</v>
       </c>
       <c r="B4" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>128369610</v>
       </c>
       <c r="B5" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128369619</v>
+        <v>128369627</v>
       </c>
       <c r="B6" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545518</v>
+        <v>545576</v>
       </c>
       <c r="R6" t="n">
-        <v>6960573</v>
+        <v>6960564</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128369627</v>
+        <v>128369619</v>
       </c>
       <c r="B7" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545576</v>
+        <v>545518</v>
       </c>
       <c r="R7" t="n">
-        <v>6960564</v>
+        <v>6960573</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1308,7 +1308,7 @@
         <v>128369616</v>
       </c>
       <c r="B8" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,7 +1409,7 @@
         <v>128369615</v>
       </c>
       <c r="B9" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>128369614</v>
       </c>
       <c r="B10" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>128369611</v>
       </c>
       <c r="B11" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>128369621</v>
       </c>
       <c r="B12" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>128369620</v>
       </c>
       <c r="B13" t="n">
-        <v>90526</v>
+        <v>90536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>128369626</v>
       </c>
       <c r="B14" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>128369624</v>
       </c>
       <c r="B15" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>128369623</v>
       </c>
       <c r="B16" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>128369618</v>
       </c>
       <c r="B17" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>128369613</v>
       </c>
       <c r="B18" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>128369617</v>
       </c>
       <c r="B19" t="n">
-        <v>78782</v>
+        <v>78786</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>128369622</v>
       </c>
       <c r="B20" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>128369625</v>
       </c>
       <c r="B21" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>128369609</v>
       </c>
       <c r="B22" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -800,32 +800,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369628</v>
+        <v>128369612</v>
       </c>
       <c r="B3" t="n">
-        <v>96878</v>
+        <v>92794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545520</v>
+        <v>545441</v>
       </c>
       <c r="R3" t="n">
-        <v>6960544</v>
+        <v>6960551</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128369612</v>
+        <v>128369628</v>
       </c>
       <c r="B4" t="n">
-        <v>92794</v>
+        <v>96878</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545441</v>
+        <v>545520</v>
       </c>
       <c r="R4" t="n">
-        <v>6960551</v>
+        <v>6960544</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128369627</v>
+        <v>128369619</v>
       </c>
       <c r="B6" t="n">
         <v>92794</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545576</v>
+        <v>545518</v>
       </c>
       <c r="R6" t="n">
-        <v>6960564</v>
+        <v>6960573</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1204,7 +1204,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128369619</v>
+        <v>128369627</v>
       </c>
       <c r="B7" t="n">
         <v>92794</v>
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545518</v>
+        <v>545576</v>
       </c>
       <c r="R7" t="n">
-        <v>6960573</v>
+        <v>6960564</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1810,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128369620</v>
+        <v>128369626</v>
       </c>
       <c r="B13" t="n">
-        <v>90536</v>
+        <v>78877</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1821,21 +1821,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545519</v>
+        <v>545578</v>
       </c>
       <c r="R13" t="n">
-        <v>6960567</v>
+        <v>6960574</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1911,32 +1911,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128369626</v>
+        <v>128369624</v>
       </c>
       <c r="B14" t="n">
-        <v>78877</v>
+        <v>92794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545578</v>
+        <v>545590</v>
       </c>
       <c r="R14" t="n">
-        <v>6960574</v>
+        <v>6960568</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2012,32 +2012,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128369624</v>
+        <v>128369620</v>
       </c>
       <c r="B15" t="n">
-        <v>92794</v>
+        <v>90536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545590</v>
+        <v>545519</v>
       </c>
       <c r="R15" t="n">
-        <v>6960568</v>
+        <v>6960567</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2214,7 +2214,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128369618</v>
+        <v>128369613</v>
       </c>
       <c r="B17" t="n">
         <v>92794</v>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545491</v>
+        <v>545435</v>
       </c>
       <c r="R17" t="n">
-        <v>6960549</v>
+        <v>6960538</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2315,7 +2315,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128369613</v>
+        <v>128369618</v>
       </c>
       <c r="B18" t="n">
         <v>92794</v>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545435</v>
+        <v>545491</v>
       </c>
       <c r="R18" t="n">
-        <v>6960538</v>
+        <v>6960549</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -800,32 +800,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369612</v>
+        <v>128369628</v>
       </c>
       <c r="B3" t="n">
-        <v>92794</v>
+        <v>96878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545441</v>
+        <v>545520</v>
       </c>
       <c r="R3" t="n">
-        <v>6960551</v>
+        <v>6960544</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128369628</v>
+        <v>128369612</v>
       </c>
       <c r="B4" t="n">
-        <v>96878</v>
+        <v>92794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545520</v>
+        <v>545441</v>
       </c>
       <c r="R4" t="n">
-        <v>6960544</v>
+        <v>6960551</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -1002,7 +1002,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128369610</v>
+        <v>128369619</v>
       </c>
       <c r="B5" t="n">
         <v>92794</v>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545456</v>
+        <v>545518</v>
       </c>
       <c r="R5" t="n">
-        <v>6960552</v>
+        <v>6960573</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128369619</v>
+        <v>128369610</v>
       </c>
       <c r="B6" t="n">
         <v>92794</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545518</v>
+        <v>545456</v>
       </c>
       <c r="R6" t="n">
-        <v>6960573</v>
+        <v>6960552</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1810,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128369626</v>
+        <v>128369620</v>
       </c>
       <c r="B13" t="n">
-        <v>78877</v>
+        <v>90536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1821,21 +1821,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545578</v>
+        <v>545519</v>
       </c>
       <c r="R13" t="n">
-        <v>6960574</v>
+        <v>6960567</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128369620</v>
+        <v>128369626</v>
       </c>
       <c r="B15" t="n">
-        <v>90536</v>
+        <v>78877</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545519</v>
+        <v>545578</v>
       </c>
       <c r="R15" t="n">
-        <v>6960567</v>
+        <v>6960574</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2214,7 +2214,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128369613</v>
+        <v>128369618</v>
       </c>
       <c r="B17" t="n">
         <v>92794</v>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545435</v>
+        <v>545491</v>
       </c>
       <c r="R17" t="n">
-        <v>6960538</v>
+        <v>6960549</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2315,7 +2315,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128369618</v>
+        <v>128369613</v>
       </c>
       <c r="B18" t="n">
         <v>92794</v>
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545491</v>
+        <v>545435</v>
       </c>
       <c r="R18" t="n">
-        <v>6960549</v>
+        <v>6960538</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128369628</v>
       </c>
       <c r="B3" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>128369612</v>
       </c>
       <c r="B4" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128369619</v>
+        <v>128369610</v>
       </c>
       <c r="B5" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545518</v>
+        <v>545456</v>
       </c>
       <c r="R5" t="n">
-        <v>6960573</v>
+        <v>6960552</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128369610</v>
+        <v>128369619</v>
       </c>
       <c r="B6" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545456</v>
+        <v>545518</v>
       </c>
       <c r="R6" t="n">
-        <v>6960552</v>
+        <v>6960573</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1207,7 +1207,7 @@
         <v>128369627</v>
       </c>
       <c r="B7" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>128369616</v>
       </c>
       <c r="B8" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,10 +1406,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128369615</v>
+        <v>128369614</v>
       </c>
       <c r="B9" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545483</v>
+        <v>545454</v>
       </c>
       <c r="R9" t="n">
-        <v>6960539</v>
+        <v>6960547</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128369614</v>
+        <v>128369615</v>
       </c>
       <c r="B10" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545454</v>
+        <v>545483</v>
       </c>
       <c r="R10" t="n">
-        <v>6960547</v>
+        <v>6960539</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,7 +1611,7 @@
         <v>128369611</v>
       </c>
       <c r="B11" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>128369621</v>
       </c>
       <c r="B12" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1810,32 +1810,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128369620</v>
+        <v>128369624</v>
       </c>
       <c r="B13" t="n">
-        <v>90536</v>
+        <v>92798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545519</v>
+        <v>545590</v>
       </c>
       <c r="R13" t="n">
-        <v>6960567</v>
+        <v>6960568</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1911,32 +1911,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128369624</v>
+        <v>128369620</v>
       </c>
       <c r="B14" t="n">
-        <v>92794</v>
+        <v>90540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545590</v>
+        <v>545519</v>
       </c>
       <c r="R14" t="n">
-        <v>6960568</v>
+        <v>6960567</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2015,7 +2015,7 @@
         <v>128369626</v>
       </c>
       <c r="B15" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>128369623</v>
       </c>
       <c r="B16" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>128369618</v>
       </c>
       <c r="B17" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>128369613</v>
       </c>
       <c r="B18" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>128369617</v>
       </c>
       <c r="B19" t="n">
-        <v>78786</v>
+        <v>78790</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>128369622</v>
       </c>
       <c r="B20" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>128369625</v>
       </c>
       <c r="B21" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>128369609</v>
       </c>
       <c r="B22" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -800,32 +800,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369628</v>
+        <v>128369612</v>
       </c>
       <c r="B3" t="n">
-        <v>96882</v>
+        <v>92798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545520</v>
+        <v>545441</v>
       </c>
       <c r="R3" t="n">
-        <v>6960544</v>
+        <v>6960551</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -901,32 +901,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128369612</v>
+        <v>128369628</v>
       </c>
       <c r="B4" t="n">
-        <v>92798</v>
+        <v>96882</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -940,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545441</v>
+        <v>545520</v>
       </c>
       <c r="R4" t="n">
-        <v>6960551</v>
+        <v>6960544</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>128369612</v>
       </c>
       <c r="B3" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>128369628</v>
       </c>
       <c r="B4" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>128369610</v>
       </c>
       <c r="B5" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>128369619</v>
       </c>
       <c r="B6" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>128369627</v>
       </c>
       <c r="B7" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>128369616</v>
       </c>
       <c r="B8" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,10 +1406,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128369614</v>
+        <v>128369615</v>
       </c>
       <c r="B9" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545454</v>
+        <v>545483</v>
       </c>
       <c r="R9" t="n">
-        <v>6960547</v>
+        <v>6960539</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128369615</v>
+        <v>128369614</v>
       </c>
       <c r="B10" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545483</v>
+        <v>545454</v>
       </c>
       <c r="R10" t="n">
-        <v>6960539</v>
+        <v>6960547</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1611,7 +1611,7 @@
         <v>128369611</v>
       </c>
       <c r="B11" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>128369621</v>
       </c>
       <c r="B12" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>128369624</v>
       </c>
       <c r="B13" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>128369620</v>
       </c>
       <c r="B14" t="n">
-        <v>90540</v>
+        <v>90545</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>128369626</v>
       </c>
       <c r="B15" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>128369623</v>
       </c>
       <c r="B16" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>128369618</v>
       </c>
       <c r="B17" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>128369613</v>
       </c>
       <c r="B18" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>128369617</v>
       </c>
       <c r="B19" t="n">
-        <v>78790</v>
+        <v>78695</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
         <v>128369622</v>
       </c>
       <c r="B20" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>128369625</v>
       </c>
       <c r="B21" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         <v>128369609</v>
       </c>
       <c r="B22" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104000202</v>
+        <v>104000137</v>
       </c>
       <c r="B2" t="n">
-        <v>90214</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2051</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Småmyrorna, Jmt</t>
+          <t>Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545563</v>
+        <v>545578</v>
       </c>
       <c r="R2" t="n">
-        <v>6960532</v>
+        <v>6960513</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +764,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -800,32 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128369612</v>
+        <v>128369628</v>
       </c>
       <c r="B3" t="n">
-        <v>92803</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545441</v>
+        <v>545520</v>
       </c>
       <c r="R3" t="n">
-        <v>6960551</v>
+        <v>6960544</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -901,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128369628</v>
+        <v>128369617</v>
       </c>
       <c r="B4" t="n">
-        <v>96889</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -940,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545520</v>
+        <v>545487</v>
       </c>
       <c r="R4" t="n">
-        <v>6960544</v>
+        <v>6960539</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1002,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128369610</v>
+        <v>128369620</v>
       </c>
       <c r="B5" t="n">
-        <v>92803</v>
+        <v>90932</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1041,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545456</v>
+        <v>545519</v>
       </c>
       <c r="R5" t="n">
-        <v>6960552</v>
+        <v>6960567</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,52 +1094,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128369619</v>
+        <v>104000202</v>
       </c>
       <c r="B6" t="n">
-        <v>92803</v>
+        <v>91394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>2051</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gustavsnäs, Jmt</t>
+          <t>Småmyrorna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>545518</v>
+        <v>545563</v>
       </c>
       <c r="R6" t="n">
-        <v>6960573</v>
+        <v>6960532</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1172,12 +1162,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1186,32 +1186,42 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128369627</v>
+        <v>128369609</v>
       </c>
       <c r="B7" t="n">
-        <v>92803</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1243,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545576</v>
+        <v>545443</v>
       </c>
       <c r="R7" t="n">
-        <v>6960564</v>
+        <v>6960571</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1305,10 +1315,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128369616</v>
+        <v>128369610</v>
       </c>
       <c r="B8" t="n">
-        <v>79648</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1316,21 +1326,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1344,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>545485</v>
+        <v>545456</v>
       </c>
       <c r="R8" t="n">
-        <v>6960542</v>
+        <v>6960552</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1406,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128369615</v>
+        <v>128369611</v>
       </c>
       <c r="B9" t="n">
-        <v>78786</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1417,21 +1427,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1445,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545483</v>
+        <v>545452</v>
       </c>
       <c r="R9" t="n">
-        <v>6960539</v>
+        <v>6960544</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1507,10 +1517,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128369614</v>
+        <v>128369612</v>
       </c>
       <c r="B10" t="n">
-        <v>78786</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,21 +1528,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1546,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>545454</v>
+        <v>545441</v>
       </c>
       <c r="R10" t="n">
-        <v>6960547</v>
+        <v>6960551</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1608,14 +1618,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128369611</v>
+        <v>128369613</v>
       </c>
       <c r="B11" t="n">
-        <v>92803</v>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1647,10 +1657,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>545452</v>
+        <v>545435</v>
       </c>
       <c r="R11" t="n">
-        <v>6960544</v>
+        <v>6960538</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1709,14 +1719,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128369621</v>
+        <v>128369618</v>
       </c>
       <c r="B12" t="n">
-        <v>92803</v>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1748,10 +1758,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>545545</v>
+        <v>545491</v>
       </c>
       <c r="R12" t="n">
-        <v>6960571</v>
+        <v>6960549</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1810,14 +1820,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128369624</v>
+        <v>128369619</v>
       </c>
       <c r="B13" t="n">
-        <v>92803</v>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1849,10 +1859,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>545590</v>
+        <v>545518</v>
       </c>
       <c r="R13" t="n">
-        <v>6960568</v>
+        <v>6960573</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1911,10 +1921,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128369620</v>
+        <v>128369621</v>
       </c>
       <c r="B14" t="n">
-        <v>90545</v>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1922,21 +1932,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1950,10 +1960,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>545519</v>
+        <v>545545</v>
       </c>
       <c r="R14" t="n">
-        <v>6960567</v>
+        <v>6960571</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2012,10 +2022,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128369626</v>
+        <v>128369622</v>
       </c>
       <c r="B15" t="n">
-        <v>78786</v>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,21 +2033,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2051,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>545578</v>
+        <v>545561</v>
       </c>
       <c r="R15" t="n">
-        <v>6960574</v>
+        <v>6960584</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2116,11 +2126,11 @@
         <v>128369623</v>
       </c>
       <c r="B16" t="n">
-        <v>92803</v>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2214,14 +2224,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128369618</v>
+        <v>128369624</v>
       </c>
       <c r="B17" t="n">
-        <v>92803</v>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2253,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>545491</v>
+        <v>545590</v>
       </c>
       <c r="R17" t="n">
-        <v>6960549</v>
+        <v>6960568</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2315,14 +2325,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128369613</v>
+        <v>128369625</v>
       </c>
       <c r="B18" t="n">
-        <v>92803</v>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2354,10 +2364,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>545435</v>
+        <v>545585</v>
       </c>
       <c r="R18" t="n">
-        <v>6960538</v>
+        <v>6960570</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2416,10 +2426,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128369617</v>
+        <v>128369627</v>
       </c>
       <c r="B19" t="n">
-        <v>78695</v>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2427,21 +2437,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2455,10 +2465,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545487</v>
+        <v>545576</v>
       </c>
       <c r="R19" t="n">
-        <v>6960539</v>
+        <v>6960564</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2517,10 +2527,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128369622</v>
+        <v>104000098</v>
       </c>
       <c r="B20" t="n">
-        <v>92803</v>
+        <v>92869</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2528,41 +2538,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>4769</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gustavsnäs, Jmt</t>
+          <t>Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>545561</v>
+        <v>545437</v>
       </c>
       <c r="R20" t="n">
-        <v>6960584</v>
+        <v>6960643</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2586,12 +2592,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2602,48 +2618,57 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128369625</v>
+        <v>128369614</v>
       </c>
       <c r="B21" t="n">
-        <v>92803</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2657,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>545585</v>
+        <v>545454</v>
       </c>
       <c r="R21" t="n">
-        <v>6960570</v>
+        <v>6960547</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2719,32 +2744,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128369609</v>
+        <v>128369615</v>
       </c>
       <c r="B22" t="n">
-        <v>92803</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2758,10 +2783,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>545443</v>
+        <v>545483</v>
       </c>
       <c r="R22" t="n">
-        <v>6960571</v>
+        <v>6960539</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2817,6 +2842,208 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128369626</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>545578</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6960574</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128369616</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>545485</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6960542</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34300-2025 artfynd.xlsx
+++ b/artfynd/A 34300-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000137</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369628</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369617</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369620</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000202</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1312,6 +1342,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369609</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1413,6 +1448,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369610</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1514,6 +1554,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369611</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369612</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1716,6 +1766,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369613</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1817,6 +1872,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369618</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1918,6 +1978,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369619</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2019,6 +2084,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369621</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2120,6 +2190,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369622</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2221,6 +2296,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369623</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2322,6 +2402,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369624</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2423,6 +2508,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369625</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2524,6 +2614,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369627</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2640,6 +2735,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104000098</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2741,6 +2841,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369614</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2842,6 +2947,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369615</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2943,6 +3053,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369626</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3044,8 +3159,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369616</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>